--- a/virtual-physics-lab/app/dl/NYJC_Q1_Tpendulum.xlsx
+++ b/virtual-physics-lab/app/dl/NYJC_Q1_Tpendulum.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -86,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -95,6 +97,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -656,7 +659,7 @@
       <c r="A6" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>1.685</v>
       </c>
     </row>
@@ -664,7 +667,7 @@
       <c r="A7" s="5" t="n">
         <v>196</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>2.373</v>
       </c>
     </row>
@@ -672,7 +675,7 @@
       <c r="A8" s="5" t="n">
         <v>484</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>3.418</v>
       </c>
     </row>
@@ -680,7 +683,7 @@
       <c r="A9" s="5" t="n">
         <v>576</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>3.782</v>
       </c>
     </row>
@@ -688,7 +691,7 @@
       <c r="A10" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>1.927</v>
       </c>
     </row>
@@ -696,8 +699,8 @@
       <c r="A11" s="5" t="n">
         <v>324</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>2.8</v>
+      <c r="B11" s="6" t="n">
+        <v>2.799</v>
       </c>
     </row>
   </sheetData>
@@ -766,7 +769,7 @@
       <c r="A6" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>1.685</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -774,7 +777,7 @@
           <t>a = gradient</t>
         </is>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <f>SLOPE(B6:B11,A6:A11)</f>
         <v/>
       </c>
@@ -788,7 +791,7 @@
       <c r="A7" s="5" t="n">
         <v>196</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>2.373</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -796,7 +799,7 @@
           <t>b = intercept</t>
         </is>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <f>INTERCEPT(B6:B11,A6:A11)</f>
         <v/>
       </c>
@@ -810,7 +813,7 @@
       <c r="A8" s="5" t="n">
         <v>484</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>3.418</v>
       </c>
     </row>
@@ -818,7 +821,7 @@
       <c r="A9" s="5" t="n">
         <v>576</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>3.782</v>
       </c>
     </row>
@@ -826,7 +829,7 @@
       <c r="A10" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>1.927</v>
       </c>
     </row>
@@ -834,8 +837,8 @@
       <c r="A11" s="5" t="n">
         <v>324</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>2.8</v>
+      <c r="B11" s="6" t="n">
+        <v>2.799</v>
       </c>
     </row>
   </sheetData>
